--- a/dcf/CIEN.xlsx
+++ b/dcf/CIEN.xlsx
@@ -849,7 +849,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-08</t>
         </is>
       </c>
     </row>
@@ -1105,25 +1105,25 @@
         </is>
       </c>
       <c r="B4" s="52" t="n">
-        <v>0.08246991495106738</v>
+        <v>0.08246324102042496</v>
       </c>
       <c r="C4" s="52" t="n">
-        <v>0.08746991495106739</v>
+        <v>0.08746324102042496</v>
       </c>
       <c r="D4" s="52" t="n">
-        <v>0.09246991495106738</v>
+        <v>0.09246324102042495</v>
       </c>
       <c r="E4" s="52" t="n">
-        <v>0.09746991495106738</v>
+        <v>0.09746324102042496</v>
       </c>
       <c r="F4" s="52" t="n">
-        <v>0.1024699149510674</v>
+        <v>0.102463241020425</v>
       </c>
       <c r="G4" s="52" t="n">
-        <v>0.1074699149510674</v>
+        <v>0.107463241020425</v>
       </c>
       <c r="H4" s="52" t="n">
-        <v>0.1124699149510674</v>
+        <v>0.112463241020425</v>
       </c>
     </row>
     <row r="5">
@@ -1131,25 +1131,25 @@
         <v>8</v>
       </c>
       <c r="B5" s="54" t="n">
-        <v>132.242965561028</v>
+        <v>104.7714466858347</v>
       </c>
       <c r="C5" s="54" t="n">
-        <v>127.1255870176897</v>
+        <v>100.8013433369867</v>
       </c>
       <c r="D5" s="54" t="n">
-        <v>122.2427448871171</v>
+        <v>97.01161767222254</v>
       </c>
       <c r="E5" s="54" t="n">
-        <v>117.5823932937195</v>
+        <v>93.39304329450978</v>
       </c>
       <c r="F5" s="54" t="n">
-        <v>113.133163580668</v>
+        <v>89.93691136288682</v>
       </c>
       <c r="G5" s="54" t="n">
-        <v>108.8843231545747</v>
+        <v>86.63499918173525</v>
       </c>
       <c r="H5" s="54" t="n">
-        <v>104.8257370113614</v>
+        <v>83.4795408346645</v>
       </c>
     </row>
     <row r="6">
@@ -1157,25 +1157,25 @@
         <v>9</v>
       </c>
       <c r="B6" s="54" t="n">
-        <v>142.3210768211119</v>
+        <v>112.4361624772735</v>
       </c>
       <c r="C6" s="54" t="n">
-        <v>136.7497947320567</v>
+        <v>108.1208493469276</v>
       </c>
       <c r="D6" s="54" t="n">
-        <v>131.4354353668109</v>
+        <v>104.0029395878572</v>
       </c>
       <c r="E6" s="54" t="n">
-        <v>126.3647537903281</v>
+        <v>100.0722948648019</v>
       </c>
       <c r="F6" s="54" t="n">
-        <v>121.525251552372</v>
+        <v>96.31934707880571</v>
       </c>
       <c r="G6" s="54" t="n">
-        <v>116.9051312422399</v>
+        <v>92.73506369374776</v>
       </c>
       <c r="H6" s="54" t="n">
-        <v>112.4932540080919</v>
+        <v>89.31091532303995</v>
       </c>
     </row>
     <row r="7">
@@ -1183,25 +1183,25 @@
         <v>10</v>
       </c>
       <c r="B7" s="54" t="n">
-        <v>152.3991880811957</v>
+        <v>120.1008782687123</v>
       </c>
       <c r="C7" s="54" t="n">
-        <v>146.3740024464236</v>
+        <v>115.4403553568685</v>
       </c>
       <c r="D7" s="54" t="n">
-        <v>140.6281258465048</v>
+        <v>110.9942615034918</v>
       </c>
       <c r="E7" s="54" t="n">
-        <v>135.1471142869367</v>
+        <v>106.751546435094</v>
       </c>
       <c r="F7" s="54" t="n">
-        <v>129.9173395240759</v>
+        <v>102.7017827947246</v>
       </c>
       <c r="G7" s="54" t="n">
-        <v>124.9259393299052</v>
+        <v>98.8351282057603</v>
       </c>
       <c r="H7" s="54" t="n">
-        <v>120.1607710048223</v>
+        <v>95.1422898114154</v>
       </c>
     </row>
     <row r="8">
@@ -1209,25 +1209,25 @@
         <v>11</v>
       </c>
       <c r="B8" s="54" t="n">
-        <v>162.4772993412796</v>
+        <v>127.7655940601512</v>
       </c>
       <c r="C8" s="54" t="n">
-        <v>155.9982101607906</v>
+        <v>122.7598613668093</v>
       </c>
       <c r="D8" s="54" t="n">
-        <v>149.8208163261987</v>
+        <v>117.9855834191265</v>
       </c>
       <c r="E8" s="55" t="n">
-        <v>143.9294747835453</v>
+        <v>113.4307980053861</v>
       </c>
       <c r="F8" s="54" t="n">
-        <v>138.3094274957799</v>
+        <v>109.0842185106435</v>
       </c>
       <c r="G8" s="54" t="n">
-        <v>132.9467474175704</v>
+        <v>104.9351927177728</v>
       </c>
       <c r="H8" s="54" t="n">
-        <v>127.8282880015528</v>
+        <v>100.9736642997908</v>
       </c>
     </row>
     <row r="9">
@@ -1235,25 +1235,25 @@
         <v>12</v>
       </c>
       <c r="B9" s="54" t="n">
-        <v>172.5554106013635</v>
+        <v>135.43030985159</v>
       </c>
       <c r="C9" s="54" t="n">
-        <v>165.6224178751576</v>
+        <v>130.0793673767502</v>
       </c>
       <c r="D9" s="54" t="n">
-        <v>159.0135068058926</v>
+        <v>124.9769053347611</v>
       </c>
       <c r="E9" s="54" t="n">
-        <v>152.711835280154</v>
+        <v>120.1100495756782</v>
       </c>
       <c r="F9" s="54" t="n">
-        <v>146.7015154674838</v>
+        <v>115.4666542265624</v>
       </c>
       <c r="G9" s="54" t="n">
-        <v>140.9675555052356</v>
+        <v>111.0352572297853</v>
       </c>
       <c r="H9" s="54" t="n">
-        <v>135.4958049982833</v>
+        <v>106.8050387881663</v>
       </c>
     </row>
     <row r="10">
@@ -1261,25 +1261,25 @@
         <v>13</v>
       </c>
       <c r="B10" s="54" t="n">
-        <v>182.6335218614473</v>
+        <v>143.0950256430288</v>
       </c>
       <c r="C10" s="54" t="n">
-        <v>175.2466255895245</v>
+        <v>137.3988733866911</v>
       </c>
       <c r="D10" s="54" t="n">
-        <v>168.2061972855864</v>
+        <v>131.9682272503958</v>
       </c>
       <c r="E10" s="54" t="n">
-        <v>161.4941957767626</v>
+        <v>126.7893011459703</v>
       </c>
       <c r="F10" s="54" t="n">
-        <v>155.0936034391878</v>
+        <v>121.8490899424812</v>
       </c>
       <c r="G10" s="54" t="n">
-        <v>148.9883635929008</v>
+        <v>117.1353217417979</v>
       </c>
       <c r="H10" s="54" t="n">
-        <v>143.1633219950138</v>
+        <v>112.6364132765417</v>
       </c>
     </row>
     <row r="11">
@@ -1287,25 +1287,25 @@
         <v>14</v>
       </c>
       <c r="B11" s="54" t="n">
-        <v>192.7116331215312</v>
+        <v>150.7597414344677</v>
       </c>
       <c r="C11" s="54" t="n">
-        <v>184.8708333038915</v>
+        <v>144.7183793966319</v>
       </c>
       <c r="D11" s="54" t="n">
-        <v>177.3988877652803</v>
+        <v>138.9595491660304</v>
       </c>
       <c r="E11" s="54" t="n">
-        <v>170.2765562733712</v>
+        <v>133.4685527162624</v>
       </c>
       <c r="F11" s="54" t="n">
-        <v>163.4856914108918</v>
+        <v>128.2315256584001</v>
       </c>
       <c r="G11" s="54" t="n">
-        <v>157.009171680566</v>
+        <v>123.2353862538104</v>
       </c>
       <c r="H11" s="54" t="n">
-        <v>150.8308389917443</v>
+        <v>118.4677877649172</v>
       </c>
     </row>
     <row r="13">
@@ -1315,7 +1315,7 @@
         </is>
       </c>
       <c r="B13" s="54" t="n">
-        <v>422.4599914550781</v>
+        <v>420.6099853515625</v>
       </c>
     </row>
     <row r="14">
@@ -1325,7 +1325,7 @@
         </is>
       </c>
       <c r="B14" s="56" t="n">
-        <v>0.09746991495106738</v>
+        <v>0.09746324102042496</v>
       </c>
       <c r="C14" s="57" t="n">
         <v>11</v>
@@ -1671,7 +1671,7 @@
         </is>
       </c>
       <c r="I8" s="49" t="n">
-        <v>1.110889048660907</v>
+        <v>1.123425202682902</v>
       </c>
       <c r="K8" s="25">
         <f>MAX(-0.05,NORMINV(RAND(),$C$6,$D$6))</f>
@@ -24410,7 +24410,7 @@
         </is>
       </c>
       <c r="B48" s="23" t="n">
-        <v>422.4599914550781</v>
+        <v>420.6099853515625</v>
       </c>
     </row>
     <row r="49">
@@ -24420,7 +24420,7 @@
         </is>
       </c>
       <c r="B49" s="20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
@@ -24572,13 +24572,13 @@
         </is>
       </c>
       <c r="B58" s="28" t="n">
-        <v>143.9294747835453</v>
+        <v>113.4307980053861</v>
       </c>
       <c r="C58" s="28" t="n">
-        <v>213.3070933561625</v>
+        <v>164.102140708319</v>
       </c>
       <c r="D58" s="28" t="n">
-        <v>93.80630083231559</v>
+        <v>75.78697703712461</v>
       </c>
     </row>
     <row r="59">
